--- a/questionnaire_templates/025_lighting_design_feedback_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/025_lighting_design_feedback_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How would you rate our service?</t>
+          <t>Select One 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,92 +1194,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,306 +1313,204 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>for_residential</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>For residential</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>for_commercial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>For commercial</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>for_residential</t>
+          <t>for_industrial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>For residential</t>
+          <t>For industrial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>for_commercial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>For commercial</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>for_industrial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>For industrial</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
